--- a/mad-map-data-v2.xlsx
+++ b/mad-map-data-v2.xlsx
@@ -642,10 +642,11 @@
     <row r="2">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>Régimen sin áreas-MAD: Líneas troncales sostenidas por Laboratorios + sublíneas + temas.</t>
-        </is>
-      </c>
-    </row>
+          <t>Régimen de dos líneas de investigación (septiembre 2026), cada una con polo teórico y polo proyectual, sostenidas por Laboratorios + sublíneas + temas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="16" customHeight="1" s="24">
       <c r="A4" s="26" t="inlineStr">
         <is>
@@ -656,7 +657,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Línea (4 troncales)</t>
+          <t>Línea (2)</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -749,6 +750,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="16" customHeight="1" s="24">
       <c r="A14" s="26" t="inlineStr">
         <is>
@@ -859,6 +861,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -879,7 +882,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Personas, interacción y sistemas inclusivos</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
     </row>
@@ -891,19 +894,19 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Personas, interacción y sistemas inclusivos</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1" s="24">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Aconcagua Fablab</t>
+          <t>Patrimonio moderno</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Oficio, tecnologías y aprendizaje proyectual</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
     </row>
@@ -915,7 +918,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Habitar, infraestructura y ecologías territoriales</t>
+          <t>Proyecto, ciudad y ecologías del territorio</t>
         </is>
       </c>
     </row>
@@ -927,21 +930,13 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Habitar, infraestructura y ecologías territoriales</t>
+          <t>Proyecto, ciudad y ecologías del territorio</t>
         </is>
       </c>
     </row>
     <row r="10" ht="60" customHeight="1" s="24">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Patrimonio moderno</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Teoría e historia de la arquitectura y el diseño</t>
-        </is>
-      </c>
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2067,6 +2062,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -2087,12 +2083,12 @@
     <row r="5" ht="60" customHeight="1" s="24">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Personas, interacción y sistemas inclusivos</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Investigación proyectual</t>
+          <t>Historiografía</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -2104,7 +2100,7 @@
     <row r="6" ht="60" customHeight="1" s="24">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Personas, interacción y sistemas inclusivos</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -2114,19 +2110,19 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>presente</t>
+          <t>predominante</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1" s="24">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Habitar, infraestructura y ecologías territoriales</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Teoría crítica</t>
+          <t>Investigación proyectual</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -2138,29 +2134,29 @@
     <row r="8" ht="60" customHeight="1" s="24">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Habitar, infraestructura y ecologías territoriales</t>
+          <t>Proyecto, ciudad y ecologías del territorio</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Investigación proyectual</t>
+          <t>Teoría crítica</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>presente</t>
+          <t>predominante</t>
         </is>
       </c>
     </row>
     <row r="9" ht="60" customHeight="1" s="24">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Teoría e historia de la arquitectura y el diseño</t>
+          <t>Proyecto, ciudad y ecologías del territorio</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Historiografía</t>
+          <t>Investigación proyectual</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -2172,36 +2168,24 @@
     <row r="10" ht="60" customHeight="1" s="24">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Teoría e historia de la arquitectura y el diseño</t>
+          <t>Proyecto, ciudad y ecologías del territorio</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Teoría crítica</t>
+          <t>Historiografía</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>predominante</t>
+          <t>presente</t>
         </is>
       </c>
     </row>
     <row r="11" ht="60" customHeight="1" s="24">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Oficio, tecnologías y aprendizaje proyectual</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Investigación proyectual</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>predominante</t>
-        </is>
-      </c>
+      <c r="A11" s="8" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2788,6 +2772,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -2816,7 +2801,7 @@
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>El doctorado forma investigadores para quienes la obra es origen y prueba de la tesis. Esa obra, sea edificada, fabricada, escrita o dibujada, vale como argumento por sí misma, y el discurso doctoral se construye para hacerla legible y discutible. La pregunta que esa obra está llamada a argumentar es la que el programa hace suya: cómo reinventar el habitar humano. Las cuatro líneas del doctorado aportan los principios que esa pregunta convoca: la inclusión y la autonomía como condiciones de quien habita, las ecologías del territorio como condiciones de dónde, la herencia disciplinar de la e[ad] y la teoría del proyecto como condiciones desde dónde se piensa, y el oficio y los medios técnicos como condiciones con qué se hace. Doctorarse aquí es haber producido una obra capaz de sostener esos principios al ponerse a prueba y, en su mejor versión, capaz de reformularlos.</t>
+          <t>El doctorado forma investigadores para quienes la obra es origen y prueba de la tesis. Esa obra, sea edificada, fabricada, escrita o dibujada, vale como argumento por sí misma, y el discurso doctoral se construye para hacerla legible y discutible. La pregunta que esa obra está llamada a argumentar es la que el programa hace suya: cómo reinventar el habitar humano, y la responde desde el habitar poético que funda a la Escuela. Las dos líneas del doctorado investigan ese habitar en arquitectura y en diseño: una investiga acerca del proyecto, su formación, su oficio y su teoría; la otra investiga a través del proyecto, sobre la ciudad, el territorio y sus ecologías. Cada línea lleva dentro su contraparte, teórica o proyectual. Doctorarse aquí es haber producido una obra capaz de sostener esos principios al ponerse a prueba y, en su mejor versión, capaz de reformularlos.</t>
         </is>
       </c>
     </row>
@@ -5149,17 +5134,18 @@
     <row r="1" ht="18" customHeight="1" s="24">
       <c r="A1" s="25" t="inlineStr">
         <is>
-          <t>01 · Líneas troncales (4 a definir — BORRADOR)</t>
+          <t>01 · Líneas de investigación (2, propuesta septiembre 2026)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>Cada Sublínea pertenece a una Línea. Los Laboratorios pueden sostener una o varias Líneas. Borrador derivado de la hipótesis de compactación.</t>
-        </is>
-      </c>
-    </row>
+          <t>Cada Sublínea pertenece a una Línea y a un polo (teórico | proyectual). Los Laboratorios pueden sostener una o varias Líneas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -5190,17 +5176,17 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Personas, interacción y sistemas inclusivos</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Investigación sobre las condiciones de quien habita: accesibilidad e inclusión, codiseño, comunicación aumentativa y alternativa, diseño de interacción y servicios, sistemas inteligentes orientados a la diversidad funcional, la autonomía y la democracia.</t>
+          <t>Investigación acerca del proyecto de arquitectura y de diseño: cómo se forma, cómo se ejerce como oficio y desde qué teoría e historia se piensa. Acervo de la e[ad] y Ciudad Abierta, historia y crítica de la arquitectura y del diseño, teoría del proyecto y sus categorías (hospitalidad, vacío, palabra poética), espacios y medios del aprendizaje, métodos de diseño, interacción, accesibilidad, fabricación y tecnologías. Forma a quienes enseñarán arquitectura y diseño. Polo teórico e histórico y polo proyectual.</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>consolidada</t>
+          <t>propuesta 2026</t>
         </is>
       </c>
     </row>
@@ -5212,63 +5198,31 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Habitar, infraestructura y ecologías territoriales</t>
+          <t>Proyecto, ciudad y ecologías del territorio</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Investigación sobre las condiciones de dónde se habita: ciudad, urbanización, ecología política, patrimonio territorial, borde costero, infraestructura urbana, vulnerabilidad y adaptación, prácticas urbanas colectivas y reuso del territorio.</t>
+          <t>Investigación a través del proyecto de arquitectura y de diseño sobre la ciudad, el territorio y sus ecologías: urbanización, ecología política, vivienda, patrimonio, borde costero, infraestructura y equipamiento, prácticas colectivas, urbanismo afectivo, diseño social y territorial. Polo teórico (teoría urbana, ecología política, vivienda) y polo proyectual (intervención, equipamiento, investigación-acción, creación de obra).</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>consolidada</t>
+          <t>propuesta 2026</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1" s="24">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>LIN-03</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Teoría e historia de la arquitectura y el diseño</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Investigación sobre las condiciones desde dónde se piensa: acervo histórico de la e[ad] y Ciudad Abierta, historia y crítica de la arquitectura moderna, teoría del proyecto, conceptos disciplinares como hospitalidad y vacío arquitectónico.</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>consolidada</t>
-        </is>
-      </c>
+      <c r="A7" s="8" t="n"/>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1" s="24">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>LIN-04</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Oficio, tecnologías y aprendizaje proyectual</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Investigación sobre las condiciones con qué se hace y cómo se transmite: métodos de diseño, oficio, saberes técnicos, fabricación digital y transferencia tecnológica, espacios educativos y pedagogía del proyecto.</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>consolidada</t>
-        </is>
-      </c>
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5285,7 +5239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="24" min="1" max="1"/>
@@ -5305,10 +5259,11 @@
     <row r="2">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>Cada sublínea pertenece a UNA línea troncal. La asignación linea_id es BORRADOR — revisar caso por caso.</t>
-        </is>
-      </c>
-    </row>
+          <t>Cada sublínea pertenece a UNA línea y a UN polo. Reasignación de septiembre 2026 (dos líneas); revisar caso por caso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -5335,6 +5290,11 @@
           <t>notas</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>polo</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="60" customHeight="1" s="24">
       <c r="A5" s="8" t="inlineStr">
@@ -5349,7 +5309,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Personas, interacción y sistemas inclusivos</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -5358,6 +5318,11 @@
         </is>
       </c>
       <c r="E5" s="8" t="n"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="60" customHeight="1" s="24">
       <c r="A6" s="8" t="inlineStr">
@@ -5372,7 +5337,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Personas, interacción y sistemas inclusivos</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -5381,6 +5346,11 @@
         </is>
       </c>
       <c r="E6" s="8" t="n"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="30" customHeight="1" s="24">
       <c r="A7" s="8" t="inlineStr">
@@ -5395,7 +5365,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Teoría e historia de la arquitectura y el diseño</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -5404,6 +5374,11 @@
         </is>
       </c>
       <c r="E7" s="8" t="n"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="60" customHeight="1" s="24">
       <c r="A8" s="8" t="inlineStr">
@@ -5418,7 +5393,7 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Habitar, infraestructura y ecologías territoriales</t>
+          <t>Proyecto, ciudad y ecologías del territorio</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -5427,6 +5402,11 @@
         </is>
       </c>
       <c r="E8" s="8" t="n"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="60" customHeight="1" s="24">
       <c r="A9" s="8" t="inlineStr">
@@ -5441,7 +5421,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Habitar, infraestructura y ecologías territoriales</t>
+          <t>Proyecto, ciudad y ecologías del territorio</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -5450,6 +5430,11 @@
         </is>
       </c>
       <c r="E9" s="8" t="n"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="75" customHeight="1" s="24">
       <c r="A10" s="8" t="inlineStr">
@@ -5464,7 +5449,7 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Oficio, tecnologías y aprendizaje proyectual</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -5475,6 +5460,11 @@
       <c r="E10" s="8" t="inlineStr">
         <is>
           <t>migró a LIN-04 (aprendizaje proyectual)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>proyectual</t>
         </is>
       </c>
     </row>
@@ -5491,7 +5481,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Personas, interacción y sistemas inclusivos</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -5500,6 +5490,11 @@
         </is>
       </c>
       <c r="E11" s="8" t="n"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="75" customHeight="1" s="24">
       <c r="A12" s="8" t="inlineStr">
@@ -5514,7 +5509,7 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Teoría e historia de la arquitectura y el diseño</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -5523,6 +5518,11 @@
         </is>
       </c>
       <c r="E12" s="8" t="n"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="75" customHeight="1" s="24">
       <c r="A13" s="8" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Oficio, tecnologías y aprendizaje proyectual</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -5548,6 +5548,11 @@
       <c r="E13" s="8" t="inlineStr">
         <is>
           <t>migró a LIN-04</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>proyectual</t>
         </is>
       </c>
     </row>
@@ -5564,7 +5569,7 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Personas, interacción y sistemas inclusivos</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -5573,6 +5578,11 @@
         </is>
       </c>
       <c r="E14" s="8" t="n"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="60" customHeight="1" s="24">
       <c r="A15" s="8" t="inlineStr">
@@ -5587,7 +5597,7 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Personas, interacción y sistemas inclusivos</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -5596,6 +5606,11 @@
         </is>
       </c>
       <c r="E15" s="8" t="n"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="75" customHeight="1" s="24">
       <c r="A16" s="8" t="inlineStr">
@@ -5610,7 +5625,7 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Teoría e historia de la arquitectura y el diseño</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -5619,6 +5634,11 @@
         </is>
       </c>
       <c r="E16" s="8" t="n"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="75" customHeight="1" s="24">
       <c r="A17" s="8" t="inlineStr">
@@ -5633,7 +5653,7 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Teoría e historia de la arquitectura y el diseño</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -5642,6 +5662,11 @@
         </is>
       </c>
       <c r="E17" s="8" t="n"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="75" customHeight="1" s="24">
       <c r="A18" s="8" t="inlineStr">
@@ -5656,7 +5681,7 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Oficio, tecnologías y aprendizaje proyectual</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
@@ -5667,6 +5692,11 @@
       <c r="E18" s="8" t="inlineStr">
         <is>
           <t>migró a LIN-04</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>proyectual</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5713,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Oficio, tecnologías y aprendizaje proyectual</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -5694,6 +5724,11 @@
       <c r="E19" s="8" t="inlineStr">
         <is>
           <t>migró a LIN-04</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>proyectual</t>
         </is>
       </c>
     </row>
@@ -5710,7 +5745,7 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Oficio, tecnologías y aprendizaje proyectual</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -5721,6 +5756,11 @@
       <c r="E20" s="8" t="inlineStr">
         <is>
           <t>migró a LIN-04</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>proyectual</t>
         </is>
       </c>
     </row>
@@ -5737,7 +5777,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Oficio, tecnologías y aprendizaje proyectual</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -5746,6 +5786,11 @@
         </is>
       </c>
       <c r="E21" s="8" t="n"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="60" customHeight="1" s="24">
       <c r="A22" s="8" t="inlineStr">
@@ -5760,7 +5805,7 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Oficio, tecnologías y aprendizaje proyectual</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -5769,6 +5814,11 @@
         </is>
       </c>
       <c r="E22" s="8" t="n"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="75" customHeight="1" s="24">
       <c r="A23" s="8" t="inlineStr">
@@ -5783,7 +5833,7 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Oficio, tecnologías y aprendizaje proyectual</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -5794,6 +5844,11 @@
       <c r="E23" s="8" t="inlineStr">
         <is>
           <t>migró a LIN-04</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>proyectual</t>
         </is>
       </c>
     </row>
@@ -5810,7 +5865,7 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Oficio, tecnologías y aprendizaje proyectual</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -5819,6 +5874,11 @@
         </is>
       </c>
       <c r="E24" s="8" t="n"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="60" customHeight="1" s="24">
       <c r="A25" s="8" t="inlineStr">
@@ -5833,7 +5893,7 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Habitar, infraestructura y ecologías territoriales</t>
+          <t>Proyecto, ciudad y ecologías del territorio</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -5844,6 +5904,11 @@
       <c r="E25" s="8" t="inlineStr">
         <is>
           <t>podría leerse en LIN-01 según énfasis</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>teórico</t>
         </is>
       </c>
     </row>
@@ -5860,7 +5925,7 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Habitar, infraestructura y ecologías territoriales</t>
+          <t>Proyecto, ciudad y ecologías del territorio</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -5871,6 +5936,11 @@
       <c r="E26" s="8" t="inlineStr">
         <is>
           <t>transversal — colocar donde tenga más respaldo</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>proyectual</t>
         </is>
       </c>
     </row>
@@ -5887,7 +5957,7 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Oficio, tecnologías y aprendizaje proyectual</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -5898,6 +5968,11 @@
       <c r="E27" s="8" t="inlineStr">
         <is>
           <t>migró a LIN-04</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>proyectual</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5989,7 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Oficio, tecnologías y aprendizaje proyectual</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
@@ -5925,6 +6000,11 @@
       <c r="E28" s="8" t="inlineStr">
         <is>
           <t>migró a LIN-04</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>proyectual</t>
         </is>
       </c>
     </row>
@@ -5941,7 +6021,7 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Oficio, tecnologías y aprendizaje proyectual</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
@@ -5950,6 +6030,11 @@
         </is>
       </c>
       <c r="E29" s="8" t="n"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="75" customHeight="1" s="24">
       <c r="A30" s="8" t="inlineStr">
@@ -5964,7 +6049,7 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Teoría e historia de la arquitectura y el diseño</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -5973,6 +6058,11 @@
         </is>
       </c>
       <c r="E30" s="8" t="n"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="30" customHeight="1" s="24">
       <c r="A31" s="8" t="inlineStr">
@@ -5987,7 +6077,7 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Oficio, tecnologías y aprendizaje proyectual</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
@@ -5996,6 +6086,11 @@
         </is>
       </c>
       <c r="E31" s="8" t="n"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="60" customHeight="1" s="24">
       <c r="A32" s="8" t="inlineStr">
@@ -6010,7 +6105,7 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Habitar, infraestructura y ecologías territoriales</t>
+          <t>Proyecto, ciudad y ecologías del territorio</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
@@ -6019,6 +6114,11 @@
         </is>
       </c>
       <c r="E32" s="8" t="n"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="60" customHeight="1" s="24">
       <c r="A33" s="8" t="inlineStr">
@@ -6033,7 +6133,7 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Habitar, infraestructura y ecologías territoriales</t>
+          <t>Proyecto, ciudad y ecologías del territorio</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
@@ -6042,6 +6142,11 @@
         </is>
       </c>
       <c r="E33" s="8" t="n"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="60" customHeight="1" s="24">
       <c r="A34" s="8" t="inlineStr">
@@ -6056,7 +6161,7 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Habitar, infraestructura y ecologías territoriales</t>
+          <t>Proyecto, ciudad y ecologías del territorio</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -6065,6 +6170,11 @@
         </is>
       </c>
       <c r="E34" s="8" t="n"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="60" customHeight="1" s="24">
       <c r="A35" s="8" t="inlineStr">
@@ -6079,7 +6189,7 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Habitar, infraestructura y ecologías territoriales</t>
+          <t>Proyecto, ciudad y ecologías del territorio</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -6090,6 +6200,11 @@
       <c r="E35" s="8" t="inlineStr">
         <is>
           <t>nueva</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>teórico</t>
         </is>
       </c>
     </row>
@@ -6106,7 +6221,7 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Habitar, infraestructura y ecologías territoriales</t>
+          <t>Proyecto, ciudad y ecologías del territorio</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -6117,6 +6232,11 @@
       <c r="E36" s="8" t="inlineStr">
         <is>
           <t>nueva</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>teórico</t>
         </is>
       </c>
     </row>
@@ -6133,7 +6253,7 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Habitar, infraestructura y ecologías territoriales</t>
+          <t>Proyecto, ciudad y ecologías del territorio</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -6144,6 +6264,11 @@
       <c r="E37" s="8" t="inlineStr">
         <is>
           <t>nueva</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>proyectual</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6285,7 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Habitar, infraestructura y ecologías territoriales</t>
+          <t>Proyecto, ciudad y ecologías del territorio</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -6171,6 +6296,11 @@
       <c r="E38" s="8" t="inlineStr">
         <is>
           <t>nueva</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>proyectual</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6317,7 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Habitar, infraestructura y ecologías territoriales</t>
+          <t>Proyecto, ciudad y ecologías del territorio</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -6198,6 +6328,11 @@
       <c r="E39" s="8" t="inlineStr">
         <is>
           <t>nueva</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>proyectual</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6349,7 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Habitar, infraestructura y ecologías territoriales</t>
+          <t>Proyecto, ciudad y ecologías del territorio</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -6225,6 +6360,11 @@
       <c r="E40" s="8" t="inlineStr">
         <is>
           <t>nueva</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>proyectual</t>
         </is>
       </c>
     </row>
@@ -6241,7 +6381,7 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>Habitar, infraestructura y ecologías territoriales</t>
+          <t>Proyecto, ciudad y ecologías del territorio</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
@@ -6252,6 +6392,11 @@
       <c r="E41" s="8" t="inlineStr">
         <is>
           <t>nueva</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>proyectual</t>
         </is>
       </c>
     </row>
@@ -6268,7 +6413,7 @@
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Habitar, infraestructura y ecologías territoriales</t>
+          <t>Proyecto, ciudad y ecologías del territorio</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -6279,6 +6424,11 @@
       <c r="E42" s="8" t="inlineStr">
         <is>
           <t>nueva</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>proyectual</t>
         </is>
       </c>
     </row>
@@ -6295,7 +6445,7 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>Habitar, infraestructura y ecologías territoriales</t>
+          <t>Proyecto, ciudad y ecologías del territorio</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -6306,6 +6456,11 @@
       <c r="E43" s="8" t="inlineStr">
         <is>
           <t>nueva</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>teórico</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6477,7 @@
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Oficio, tecnologías y aprendizaje proyectual</t>
+          <t>Proyecto, ciudad y ecologías del territorio</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
@@ -6333,6 +6488,11 @@
       <c r="E44" s="8" t="inlineStr">
         <is>
           <t>nueva</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>proyectual</t>
         </is>
       </c>
     </row>
@@ -6349,7 +6509,7 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>Oficio, tecnologías y aprendizaje proyectual</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
@@ -6360,6 +6520,11 @@
       <c r="E45" s="8" t="inlineStr">
         <is>
           <t>nueva — núcleo Jeldes</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>proyectual</t>
         </is>
       </c>
     </row>
@@ -6376,7 +6541,7 @@
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Personas, interacción y sistemas inclusivos</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
@@ -6387,6 +6552,11 @@
       <c r="E46" s="8" t="inlineStr">
         <is>
           <t>nueva</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>proyectual</t>
         </is>
       </c>
     </row>
@@ -6403,7 +6573,7 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Oficio, tecnologías y aprendizaje proyectual</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
@@ -6414,6 +6584,11 @@
       <c r="E47" s="8" t="inlineStr">
         <is>
           <t>nueva</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>proyectual</t>
         </is>
       </c>
     </row>
@@ -6430,7 +6605,7 @@
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Habitar, infraestructura y ecologías territoriales</t>
+          <t>Proyecto, ciudad y ecologías del territorio</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
@@ -6441,6 +6616,11 @@
       <c r="E48" s="8" t="inlineStr">
         <is>
           <t>nueva</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>proyectual</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6637,7 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>Habitar, infraestructura y ecologías territoriales</t>
+          <t>Proyecto, ciudad y ecologías del territorio</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
@@ -6468,6 +6648,11 @@
       <c r="E49" s="8" t="inlineStr">
         <is>
           <t>nueva</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>proyectual</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6669,7 @@
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Oficio, tecnologías y aprendizaje proyectual</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
@@ -6495,6 +6680,11 @@
       <c r="E50" s="8" t="inlineStr">
         <is>
           <t>nueva</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>proyectual</t>
         </is>
       </c>
     </row>
@@ -6511,7 +6701,7 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>Teoría e historia de la arquitectura y el diseño</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
@@ -6522,6 +6712,11 @@
       <c r="E51" s="8" t="inlineStr">
         <is>
           <t>nueva</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>teórico</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6733,7 @@
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Teoría e historia de la arquitectura y el diseño</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
@@ -6549,6 +6744,11 @@
       <c r="E52" s="8" t="inlineStr">
         <is>
           <t>nueva</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>teórico</t>
         </is>
       </c>
     </row>
@@ -6565,7 +6765,7 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>Teoría e historia de la arquitectura y el diseño</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
@@ -6576,6 +6776,11 @@
       <c r="E53" s="8" t="inlineStr">
         <is>
           <t>nueva</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>teórico</t>
         </is>
       </c>
     </row>
@@ -6592,7 +6797,7 @@
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Teoría e historia de la arquitectura y el diseño</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
@@ -6603,6 +6808,11 @@
       <c r="E54" s="8" t="inlineStr">
         <is>
           <t>nueva</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>teórico</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6829,7 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>Teoría e historia de la arquitectura y el diseño</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
@@ -6630,6 +6840,11 @@
       <c r="E55" s="8" t="inlineStr">
         <is>
           <t>nueva</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>teórico</t>
         </is>
       </c>
     </row>
@@ -6646,7 +6861,7 @@
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Oficio, tecnologías y aprendizaje proyectual</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
@@ -6657,6 +6872,11 @@
       <c r="E56" s="8" t="inlineStr">
         <is>
           <t>nueva</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>teórico</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6893,7 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>Personas, interacción y sistemas inclusivos</t>
+          <t>Formación, oficio y teoría del proyecto</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
@@ -6684,6 +6904,11 @@
       <c r="E57" s="8" t="inlineStr">
         <is>
           <t>nueva — separa IA aplicada al diseño democrático/inclusivo de fabricación digital</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>proyectual</t>
         </is>
       </c>
     </row>

--- a/mad-map-data-v2.xlsx
+++ b/mad-map-data-v2.xlsx
@@ -24,6 +24,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16_Resumen" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17_Sello" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18_Proximidad_Tematica" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19_Proyectos" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_Productividad" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
     <definedName name="AreaNombres">OFFSET('03_Areas'!$B$5,0,0,COUNTA('03_Areas'!$B$5:$B$10000),1)</definedName>
@@ -44,7 +46,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -121,6 +123,13 @@
       <i val="1"/>
       <color rgb="FF666666"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="7">
@@ -199,7 +208,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -259,6 +268,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -646,7 +657,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="16" customHeight="1" s="24">
       <c r="A4" s="26" t="inlineStr">
         <is>
@@ -750,7 +760,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14" ht="16" customHeight="1" s="24">
       <c r="A14" s="26" t="inlineStr">
         <is>
@@ -861,7 +870,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -882,7 +890,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
     </row>
@@ -894,7 +902,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
     </row>
@@ -906,7 +914,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
     </row>
@@ -918,7 +926,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Proyecto, ciudad y ecologías del territorio</t>
+          <t>Prácticas proyectuales</t>
         </is>
       </c>
     </row>
@@ -930,7 +938,7 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Proyecto, ciudad y ecologías del territorio</t>
+          <t>Prácticas proyectuales</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2070,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -2083,7 +2090,7 @@
     <row r="5" ht="60" customHeight="1" s="24">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -2100,7 +2107,7 @@
     <row r="6" ht="60" customHeight="1" s="24">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -2117,7 +2124,7 @@
     <row r="7" ht="60" customHeight="1" s="24">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -2134,7 +2141,7 @@
     <row r="8" ht="60" customHeight="1" s="24">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Proyecto, ciudad y ecologías del territorio</t>
+          <t>Prácticas proyectuales</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -2151,7 +2158,7 @@
     <row r="9" ht="60" customHeight="1" s="24">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Proyecto, ciudad y ecologías del territorio</t>
+          <t>Prácticas proyectuales</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -2168,7 +2175,7 @@
     <row r="10" ht="60" customHeight="1" s="24">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Proyecto, ciudad y ecologías del territorio</t>
+          <t>Prácticas proyectuales</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -2268,12 +2275,12 @@
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>El brief inicial dice 4. En la elicitación apareció '3 líneas x definir'. Se trabaja con 4 BORRADOR; la 4ª (Métodos, técnicas y medios) es candidata a fusionar con LIN-01 o LIN-03 si se decide compactar a 3.</t>
+          <t>Resuelta en septiembre de 2026: dos líneas, que prolongan las áreas Extensión, Ciudad y Habitabilidad y Educación, Espacio y Aprendizaje del Magíster (ver propuesta-dos-lineas.md).</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Abierta</t>
+          <t>Resuelta</t>
         </is>
       </c>
     </row>
@@ -2285,17 +2292,17 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Nombres definitivos de las 4 Líneas</t>
+          <t>Nombres definitivos de las Líneas</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Los nombres actuales son derivados de la hipótesis de compactación. Confirmar redacción institucional (la que iría a CNA).</t>
+          <t>Resuelta el 6 oct 2026: Prácticas proyectuales (LIN-02) y Fundamentos disciplinares (LIN-01), nombres simétricos (plural que engloba + adjetivo). Reemplaza 'Intervención proyectual' (29 sep). La dimensión formativa va en la definición, no en el título.</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Abierta</t>
+          <t>Resuelta</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2779,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -5116,6 +5122,7709 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K156"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" style="24" min="1" max="1"/>
+    <col width="6" customWidth="1" style="24" min="2" max="2"/>
+    <col width="70" customWidth="1" style="24" min="3" max="3"/>
+    <col width="40" customWidth="1" style="24" min="4" max="4"/>
+    <col width="40" customWidth="1" style="24" min="5" max="5"/>
+    <col width="26" customWidth="1" style="24" min="6" max="6"/>
+    <col width="11" customWidth="1" style="24" min="7" max="7"/>
+    <col width="10" customWidth="1" style="24" min="8" max="8"/>
+    <col width="10" customWidth="1" style="24" min="9" max="9"/>
+    <col width="8" customWidth="1" style="24" min="10" max="10"/>
+    <col width="30" customWidth="1" style="24" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>19 · Proyectos de investigación y creación (2014-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Un proyecto por fila, deduplicado entre coautores. La sublínea se asignó a partir del título (confianza alta/media/baja); revisar las marcadas. Línea y polo se derivan de la sublínea. Fuente: Levantamiento de productividad 2014-2026 (planilla del equipo, oct 2026). No incluye a profesores externos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B4" s="30" t="inlineStr">
+        <is>
+          <t>año</t>
+        </is>
+      </c>
+      <c r="C4" s="30" t="inlineStr">
+        <is>
+          <t>título</t>
+        </is>
+      </c>
+      <c r="D4" s="30" t="inlineStr">
+        <is>
+          <t>investigadores</t>
+        </is>
+      </c>
+      <c r="E4" s="30" t="inlineStr">
+        <is>
+          <t>sublínea</t>
+        </is>
+      </c>
+      <c r="F4" s="30" t="inlineStr">
+        <is>
+          <t>línea</t>
+        </is>
+      </c>
+      <c r="G4" s="30" t="inlineStr">
+        <is>
+          <t>polo</t>
+        </is>
+      </c>
+      <c r="H4" s="30" t="inlineStr">
+        <is>
+          <t>ventana_2022_2026</t>
+        </is>
+      </c>
+      <c r="I4" s="30" t="inlineStr">
+        <is>
+          <t>confianza</t>
+        </is>
+      </c>
+      <c r="J4" s="30" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="K4" s="30" t="inlineStr">
+        <is>
+          <t>notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PRY-001</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Definición de parámetros espaciales para la arquitectura de la accesibilidad, aplicables en el paisaje cultural de valparaiso</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>David Luza Cornejo</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Movilidad, infraestructura urbana y equipamiento</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PRY-002</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Diseño colaborativo y Participación Ciudadana:Formulación de un marco teórico de Diseño a partir de dos experiencias de participación ciudadana.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Michèle Wilkomirsky Uribe</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Diseño para la democracia y comunicación ciudadana</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PRY-003</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Hacer lugar: experiencia de obra en las comunidades locales a partir de la integración de diseño colaborativo y fabricación digital</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Juan Carlos Jeldes Pontio</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Fabricación digital, modelado paramétrico y fablabs</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PRY-004</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Laboratorio de Fabricación Digital Móvil”. Transferencia tecnológica y experimentación en medios de Fabricación Digital para el fomento a la innovación y fortalecimiento de la Industria Creativa regional, generador de desarrollo productivo en la Región de Valparaíso.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Juan Carlos Jeldes Pontio</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Fabricación digital, modelado paramétrico y fablabs</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PRY-005</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Mobiliario Religioso de Valparaíso y su producción como expresión de sociedad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Daniela Salgado Cofré</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Diseño social, territorial y patrimonio cultural</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PRY-006</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Rediseño de las Partituras de Interacción: Formalización de un Lenguaje para la Industria de Diseño UX</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Herbert Spencer González, Katherine Exss Cid</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Diseño de interacción, servicios y experiencia de usuario</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PRY-007</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Sistema de prefabricación monomaterial liviano para viviendas económicas</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Erick Caro</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Saberes técnicos análogos</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PRY-008</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>“A pie de página”: bitácoras de Viajes y Travesías e(ad)-PUCV</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Sylvia Arriagada Cordero</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Acervo histórico de Ciudad Abierta y de la Escuela de Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PRY-009</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Aula ritual comunitaria: creación de la envolvente del vacío arquitectónico de un acto educativo en el territorio-escuela.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Rodrigo Saavedra Venegas</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Espacios de aprendizaje en contextos vulnerables</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PRY-010</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Bases para la Formulación de una Política Cultural Universitaria</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Iván Ivelic Yanes</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Industrias creativas e innovación social para el desarrollo local</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PRY-011</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Diseño escenario con características acústicas para las semanas musicales de Contulmo</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Andrés Garcés Alzamora</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Ciudad-teatro y apropiación escénica del espacio público</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PRY-012</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Estudio de la movilidad y función social en los caminos de escala intermedia en Valparaíso</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>David Luza Cornejo</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Movilidad, infraestructura urbana y equipamiento</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>PRY-013</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Las partituras de interacción como herramientas de diseño para la modelación de valor en nuevos servicios digitales</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Herbert Spencer González, Katherine Exss Cid</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Diseño de interacción, servicios y experiencia de usuario</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PRY-014</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Puesta en Valor de la Obra Poética de Godofredo Iommi M. (1917-2001)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Manuel Sanfuentes</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Poesía y oficio</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PRY-015</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Recorrido de la Cultura Material Religiosa en Valparaíso</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Daniela Salgado Cofré, Álvaro Mercado Jara</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Diseño social, territorial y patrimonio cultural</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PRY-016</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Reestructuración de línea de estudio en cuanto a referencias artísticas del campo del Diseño</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Alejandro Garretón</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Fundamentos poéticos y artísticos del diseño</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PRY-017</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Creación y realización de obras escenográficas para Teatro y Música con niños y jóvenes 2016</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Andrés Garcés Alzamora</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Ciudad-teatro y apropiación escénica del espacio público</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PRY-018</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Diseño del primer Fablab Distribuido Regional. Sistema de red de capacidades distribuidas para la innovación tecnológica a través de la fabricación digital</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Juan Carlos Jeldes Pontio</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Fabricación digital, modelado paramétrico y fablabs</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PRY-019</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Generación y transformación del espacio público de ocio urbano en Valparaíso: Paradigma entre producción y prácticas informales en la parte alta de la ciudad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Álvaro Mercado Jara</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Prácticas colectivas</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PRY-020</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Multi Plataforma colaborativa para administrar terapias fonoaudiológicas</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Michèle Wilkomirsky Uribe</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Diseño de interacción, servicios y experiencia de usuario</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PRY-021</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Plataforma Mesh de Iluminación Basada en Nodos Controlados Mediante Servicio Web</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Herbert Spencer González</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Máquinas expresivas, algoritmos y arte tecnológico</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PRY-022</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Barrio digital/territorio barrial co-diseñando los espacios de participación ciudadana. Proyecto DI 37/2017.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Michèle Wilkomirsky Uribe</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Diseño para la democracia y comunicación ciudadana</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PRY-023</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Cartografía Escénica de Valparaíso, proyecto para la difusión de espacios escénicos callejeros</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Andrés Garcés Alzamora</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Ciudad-teatro y apropiación escénica del espacio público</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PRY-024</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Diseño de una fuente tipográfca para la ead</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Alejandro Garretón</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Comunicación visual, diseño editorial y exposición material</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PRY-025</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Dispositivo Actor-Reactor como unidad material para la interacción física en espacios expositivos</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Herbert Spencer González, Marcelo Araya Aravena, Leonardo Aravena</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Máquinas expresivas, algoritmos y arte tecnológico</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PRY-026</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>El Espacio Expositivo en la Incorporación de la Interacción como Material de Diseño en la Formación Artística del Diseñador</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Marcelo Araya Aravena</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Máquinas expresivas, algoritmos y arte tecnológico</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PRY-027</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>El vacío lúdico: espacio público didáctico de estimulación, aprendizaje e identidad”</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Rodrigo Saavedra Venegas</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Espacios de estimulación temprana</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PRY-028</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Estudio y exploración espacial sensible del Caminar y su efecto en una visión de movilidad activa, a escala humana, en avenida Brasil Valparaíso.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>David Luza Cornejo</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Movilidad, infraestructura urbana y equipamiento</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PRY-029</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>I2: Investigación Inclusiva: Oportunidades para fortalecer la autodeterminación en la era digital</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Herbert Spencer González</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Accesibilidad e inclusión</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PRY-030</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Procesos colectivos de diseño: Ronda de la Ciudad Abierta</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Óscar Andrade Castro</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Formación en pensamiento y acción creativa</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PRY-031</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Artefacto sensible ludico urbano</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>David Luza Cornejo</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Mobiliario, vida cotidiana y materialidad de la obra</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PRY-032</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ações para inovação social e/ou tecnológica na América Latina</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Arturo Chicano Jiménez</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Industrias creativas e innovación social para el desarrollo local</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PRY-033</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Casiopea: Uso de las Tecnologías de Información y las Comunicaciones en el Taller</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Herbert Spencer González, Jaime Reyes Gil, David Luza Cornejo</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Medios de aprendizaje en arquitectura y diseño</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PRY-034</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Cinco intentos filosóficos de François Fédier</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Sylvia Arriagada Cordero</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Tecnología, sociedad y techné</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PRY-035</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Cualidades espaciales del edificio escolar: Luz y tamaño en la Escuela María Gaete de Arauco</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Ursula Exss Cid</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Proyecto de arquitectura escolar</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PRY-036</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Develando la urbanización Sudamericana: La noción de Mar Interior y Baldío Americano en la práctica de las Travesías de Amereida</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Álvaro Mercado Jara</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Travesías y geopoética</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PRY-037</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Diálogo de actualización en re-creación sintactica mobiliario e[ad]</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Juan Carlos Jeldes Pontio</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Mobiliario, vida cotidiana y materialidad de la obra</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PRY-038</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Fonds et Tiroirs: Co-Diseño en Tiempo Real en Arquitectura y Paisaje</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Iván Ivelic Yanes</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Naturaleza, paisaje y patrimonio natural</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PRY-039</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>I3: Investigación, Innovación e Inclusión en la PUCV</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Herbert Spencer González</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Accesibilidad e inclusión</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PRY-040</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Móvil Maker, acelerando el desarrollo de una cultura innovadora en la Región de Atacama</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Juan Carlos Jeldes Pontio</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Transferencia de medios tecnológicos con aplicación al emprendimiento local</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PRY-041</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Permeabilidad y Resistencia: ¿Cómo cambian las expresiones formales y técnicas de la artesanía? Los casos de Pomaire y Rari.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Daniela Salgado Cofré</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Diseño social, territorial y patrimonio cultural</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>PRY-042</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Red Científica Interdisciplinaria de investigación e innovación en Discapacidad Intelectual y/o del Desarrollo (REIDI)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Herbert Spencer González</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Accesibilidad e inclusión</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PRY-043</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Refiguración de un vacío lúdico: Observar y transformar la habitabilidad de un espacio público de estimulación para la primera infancia.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Rodrigo Saavedra Venegas</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Espacios de estimulación temprana</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>PRY-044</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Un territorio sub-antártico de innovación ecológico-cultural: Propuesta conceptual y arquitectónica del Complejo étnico, científico y turístico de Jetarkte</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Andrés Garcés Alzamora, Marcelo Araya Aravena</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Naturaleza, paisaje y patrimonio natural</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PRY-045</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Apoyos Visuales para la Plena Inclusión de las Personas con Discapacidad Intelectual en los Servicios Públicos en Chile</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Herbert Spencer González, Katherine Exss Cid</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Accesibilidad cognitiva y codiseño</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PRY-046</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>BUILD Confidence “Empowering vulnerable communities facing environmental risks to achieve resilience"</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Daniela Salgado Cofré</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Comunes, comunalidad y resiliencias socioecológicas</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>PRY-047</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Cualidades espaciales del edificio escolar: Colegio María Gaete de Arauco (1965)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Ursula Exss Cid</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Proyecto de arquitectura escolar</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>PRY-048</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Entre innovación y tradición: Fricciones y controversias en Pomaire y el objeto artesanal</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Daniela Salgado Cofré</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Diseño social, territorial y patrimonio cultural</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PRY-049</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Errando se aprende a errar</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Emanuela Di Felice</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Urbanismo afectivo, deriva y reuso del patrimonio</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PRY-050</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Facilitando el aprendizaje a lo largo de la vida: desafíos que plantea el envejecimiento de la población con discapacidad intelectual o del desarrollo en Chile</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Herbert Spencer González</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Diseño y vida independiente</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PRY-051</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Formas y estructuras asociadas a biopelículas bacterianas: Dilucidando los patrones autorregulados emergentes para crear construcciones resilientes</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>David Luza Cornejo</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Adaptación formal ante desastres</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>PRY-052</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>GeoHumanidades y (Bio)Geografías Creativas abordando la sustentabilidad y co-conservación a través de "Inmersión Rizomática"</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Juan Carlos Jeldes Pontio</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Comunes, comunalidad y resiliencias socioecológicas</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>PRY-053</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>LIAE-LABORATORIO INTERDISCIPLINARIO DE ARTES ESCENICAS PARA LA CREACION DE UN POEMA ESCENICO</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Andrés Garcés Alzamora</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Ciudad-teatro y apropiación escénica del espacio público</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>PRY-054</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Nuevos desafíos para Educación en Chile: Apoyos a la vida independiente de adultos con discapacidad intelectual o del desarrollo</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Herbert Spencer González, Katherine Exss Cid</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Diseño y vida independiente</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>PRY-055</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Núcleo de Investigación en Estudios de Inclusión y Accesibilidad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Herbert Spencer González, David Luza Cornejo, Katherine Exss Cid</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Accesibilidad e inclusión</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>PRY-056</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Re-presentando la extensión Sudamericana: Compilación de la geo-poética de Mar Interior en las Travesías de Amereida</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Álvaro Mercado Jara</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Travesías y geopoética</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>PRY-057</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Travesias a pueblos originarios: Extension del aula al territorio</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Rodrigo Saavedra Venegas</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Arquitectura como medio didáctico</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>PRY-058</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Amereida first volume</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Manuel Sanfuentes</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Poesía y oficio</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>PRY-059</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Americas translated place</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Manuel Sanfuentes, Isabel M. Reyes</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Travesías y geopoética</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>PRY-060</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Artefactos de diseño para la objetualización del vacío expresivo en los talleres de diseño de la Escuela de Arquitectura y Diseño PUCV.</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Alfred Thiers Jusan, Jaime Reyes Gil</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Formación en pensamiento y acción creativa</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>PRY-061</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>El aula en el territorio: Refiguraciones del espacio de aprendizaje mediante la definición de criterios arquitectónicos que ponen en valor la extensión (exterior, aire libre) del aula en el territorio.</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Rodrigo Saavedra Venegas</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Diseño de espacios educativos</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PRY-062</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>El enjambre del oficio: Configuración taxonómica de un corpus disciplinar</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Sylvia Arriagada Cordero</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Poesía y oficio</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>PRY-063</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>El grabado en la formación del diseño gráfico: La tonalidad del fotograbado en la investigación del color bajo el mar</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Alejandro Garretón</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Comunicación visual, diseño editorial y exposición material</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>PRY-064</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Elaboración de modelo de planificación de inversiones</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Lorena Herrera Ponce</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Evaluación social y políticas públicas de inversión</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>PRY-065</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Espacialidad gráfica y el acto de leer: desde el registro a la obra</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Alejandro Garretón</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Comunicación visual, diseño editorial y exposición material</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>PRY-066</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Expertos por Experiencia. El proceso de investigación inclusiva: un desafío para los nuevos tiempos</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Herbert Spencer González, Katherine Exss Cid</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Accesibilidad cognitiva y codiseño</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>PRY-067</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Investigación interdisciplinaria para pregrado: PiX como lenguaje y método accesible para el codiseño</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Katherine Exss Cid</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Accesibilidad cognitiva y codiseño</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>PRY-068</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Objeto lúdico Laberinto Coreográfico - Experiencia kinestésica del espacio arquitectónico</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Ursula Exss Cid</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Arquitectura como medio didáctico</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>PRY-069</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>PiX como lenguaje y método accesible para el co-diseño</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Katherine Exss Cid</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Accesibilidad cognitiva y codiseño</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>PRY-070</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Proyecto, resistencia y exploración tipológica en edificios escolares modernos (Chile 1940-1980)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Ursula Exss Cid</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Proyecto de arquitectura escolar</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>PRY-071</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Re-consolidación tipológica de las periferias patrimoniales obsolescentes: el caso del Cerro Monjas, Valparaíso</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Marcelo Araya Aravena</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Patrimonio arquitectónico y rehabilitación</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>PRY-072</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Rizoma: Composiciones escénicas colectivas en el territorio</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Andrés Garcés Alzamora</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Ciudad-teatro y apropiación escénica del espacio público</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>PRY-073</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Vacio lúdico de un aula al aire libre: extensión del aula de la primera infancia hacia un espacio público de estimulación temprana</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Rodrigo Saavedra Venegas</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Espacios de estimulación temprana</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>PRY-074</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Amereida - Documenta 14</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Herbert Spencer González, Manuel Sanfuentes, Daniela Salgado Cofré, Jaime Reyes Gil, Álvaro Mercado Jara, Juan Carlos Jeldes Pontio, Iván Ivelic Yanes, Andrés Garcés Alzamora, Sylvia Arriagada Cordero, Marcelo Araya Aravena, Óscar Andrade Castro</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Acervo histórico de Ciudad Abierta y de la Escuela de Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>PRY-075</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Apoyos para el autocuidado y la vida independiente de adultos con discapacidad intelectual</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Katherine Exss Cid</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Diseño y vida independiente</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>PRY-076</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Cartografía de Espacios Escénicos Urbanos de Valparaíso: Catálogo digital de espacios públicos quesean aptos para la realización de actividades artísticas escénicas y culturales en la ciudad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Andrés Garcés Alzamora</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Ciudad-teatro y apropiación escénica del espacio público</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>PRY-077</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Diseño para la enseñanza de la escritura en modalidad remota</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Herbert Spencer González</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Medios de aprendizaje en arquitectura y diseño</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>PRY-078</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Formas, vetas y re-territorialidades de las arcillas de Valparaíso</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Daniela Salgado Cofré, Álvaro Mercado Jara</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Diseño social, territorial y patrimonio cultural</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>PRY-079</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Inhabit, culture and territory: designing with community knowledge. Tools for co-evaluating and co-designing visual information for emergencies</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Michèle Wilkomirsky Uribe</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Comunicación visual, diseño editorial y exposición material</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>PRY-080</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Kinesis, la geometría Intangible entre cuerpo y lugar, Folio 635838</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Andrés Garcés Alzamora</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Ciudad-teatro y apropiación escénica del espacio público</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>PRY-081</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Kinesis: el cuerpo, los actos, el espacio arquitectónico y la extensión</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Andrés Garcés Alzamora</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Ciudad-teatro y apropiación escénica del espacio público</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>PRY-082</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Pedagogía de la luz: dispositivos arquitectónicos para el diseño y estudio de la luz natural</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Óscar Andrade Castro</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Arquitectura como medio didáctico</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>PRY-083</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Prácticas Experimentales escala 1:1; Contribuciones en la Formación, Creacion e Investigación en Arquitectura</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Iván Ivelic Yanes</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Arquitectura como medio didáctico</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>PRY-084</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Transición - Una oportunidad para la improvisación informada</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Iván Ivelic Yanes</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Formación en pensamiento y acción creativa</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>PRY-085</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Aprendizaje a través de Tecnologías de Interacción en Diseño</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Daniela Salgado Cofré, Leonardo Aravena</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Medios de aprendizaje en arquitectura y diseño</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>PRY-086</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Arquitectura moderna y ciudad: el proyecto urbano ante el desafío del desarrollo. Chile 1930-1980</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Ursula Exss Cid</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Arquitectura moderna y habitar latinoamericano</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>PRY-087</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Arquitectura y escuelas barriales de Valparaíso</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Ursula Exss Cid</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Proyecto de arquitectura escolar</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>PRY-088</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Bitácoras de vida, trabajo y estudio. Cuadernos de Fabio Cruz, Manuel Casanueva y José Balcells</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Jaime Reyes Gil</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Acervo histórico de Ciudad Abierta y de la Escuela de Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>PRY-089</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Conocimiento tácito en el estudio de la luz natural: los modelos 1:1 como estrategia de aprendizaje.</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Iván Ivelic Yanes, Óscar Andrade Castro</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Arquitectura como medio didáctico</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>PRY-090</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Crafting Methods in Design Research (Chile/Belgium)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Daniela Salgado Cofré, Álvaro Mercado Jara</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Métodos de diseño</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>PRY-091</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>DIE Incentiva en el Aula Asociativo</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Daniela Salgado Cofré, Álvaro Mercado Jara</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Medios de aprendizaje en arquitectura y diseño</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>PRY-092</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>El estudio de la luz natural como conocimiento tácito en el currículum de arquitectura</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Óscar Andrade Castro</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Arquitectura como medio didáctico</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>PRY-093</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Feria-Gradería: flexibilidad arquitectónica para la articulación social y cultural del territorio</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Rodrigo Saavedra Venegas</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Movilidad, infraestructura urbana y equipamiento</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>PRY-094</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Geografías de la transitoriedad residencial: mercados, formas y prácticas del arriendo en Chile. Fondecyt n° 1221332</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Adriana Marín Toro</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Vivienda, financiarización y políticas habitacionales</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>PRY-095</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Holistic well-being and well-living (buen vivir) in future living environments: a posthuman and indigenous land-based approach.</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Iván Ivelic Yanes</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Perspectivas decoloniales</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>PRY-096</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Humedales depuradores: Reutilizando agua para la sequía.</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Lorena Herrera Ponce</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Naturaleza, paisaje y patrimonio natural</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>PRY-097</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>La forma que habita el espacio: la obra de diseño del arquitecto Fabio Cruz Prieto (1952-2007)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Juan Carlos Jeldes Pontio, Ursula Exss Cid</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Acervo histórico de Ciudad Abierta y de la Escuela de Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>PRY-098</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Modelo de desarrollo integral para el acompañamiento de trayectorias educativas STEM/STEAM para liceos técnicos desde un enfoque de género</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Juan Carlos Jeldes Pontio</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Medios de aprendizaje en arquitectura y diseño</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>PRY-099</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Módulos trans-escalares</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Óscar Andrade Castro</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Arquitectura como medio didáctico</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>PRY-100</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Open source VR platform for accessible collaboration in the co-imagination of the future intelligent city</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Herbert Spencer González</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Accesibilidad cognitiva y codiseño</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>PRY-101</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>PICTOS: Servicio para la navegación y evaluación de la accesibilidad cognitiva de los servicios en Chile</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Herbert Spencer González, Katherine Exss Cid</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Accesibilidad cognitiva y codiseño</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>PRY-102</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Plataforma Auto Instruccional Para Determinar El Perfil Del Conocimiento Especializado Del Profesor De Matemática Y Fortalecer Aquel Conocimiento Deficiente. Proyecto Interdisciplinario PUCV-UAH-UCN, Chile; UIS, Colombia; Universidad de Oviedo, Universidad de Valladolid, España. Áreas: Matemáticas, Estadística, Ingeniería Informática, Diseño</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Michèle Wilkomirsky Uribe</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Diseño de interacción, servicios y experiencia de usuario</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>PRY-103</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Red de ciclovías para la Población Vergara</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>David Luza Cornejo</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Movilidad, infraestructura urbana y equipamiento</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>PRY-104</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Tools for co-evaluating visual information for emergencies Aotearoa/Chile</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Michèle Wilkomirsky Uribe</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Comunicación visual, diseño editorial y exposición material</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>PRY-105</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>AWEN - Método para evaluar el diseño de viviendas universalmente accesibles en entornos de realidad virtual (RV): Una iniciativa orientada a promover el derecho a la vida independiente de las personas con discapacidad</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Herbert Spencer González, Katherine Exss Cid</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Accesibilidad e inclusión</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>PRY-106</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Artefactos Especulativos: Zoom In/ Zoom out al extractivismo en el maritorio del Norte Chico</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Daniela Salgado Cofré, Álvaro Mercado Jara, Leonardo Aravena</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Urbanización, urbanismo y ecología política</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>PRY-107</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Artesanos del descarte: talleres de reutilización de cintas de riego agrícola en desuso orientados a adultos mayores de la comuna de Quillota.</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Daniela Salgado Cofré</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Diseño social, territorial y patrimonio cultural</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>PRY-108</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Bitácoras de vida, trabajo y estudio. Cuadernos de maestros de la PUCV</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Jaime Reyes Gil</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Acervo histórico de Ciudad Abierta y de la Escuela de Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>PRY-109</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Co-designing our future collective living environments: lessons from participatory design practices with indigenous communities (DI 039.453)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Iván Ivelic Yanes</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Prácticas colectivas</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>PRY-110</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Dimensión tácita de la luz natural en la práctica y formación arquitectónica: casos de la arquitectura religiosa moderna en Chile</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Óscar Andrade Castro</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Arquitectura como medio didáctico</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>PRY-111</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Diseño de un puerto inteligente y sustentable para la region de Magallanes y la Antartida Chilena</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Iván Ivelic Yanes</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Movilidad, infraestructura urbana y equipamiento</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>PRY-112</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Educando en autodeterminación al final de la vida: una propuesta formativa dirigida a personas con discapacidad intelectual que envejecen</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Herbert Spencer González, Katherine Exss Cid</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Diseño y vida independiente</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>PRY-113</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Errando se Aprende</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Emanuela Di Felice</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Urbanismo afectivo, deriva y reuso del patrimonio</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>PRY-114</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Geometria In-tangible</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Andrés Garcés Alzamora</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Ciudad-teatro y apropiación escénica del espacio público</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>PRY-115</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Kit para el estudio de la luz natural en arquitectura</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Óscar Andrade Castro</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Arquitectura como medio didáctico</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>PRY-116</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>La Inteligencia Artificial y su Inserción en el Sistema eduactivo Actual (Centenario DI 39368)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Iván Ivelic Yanes</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Sistemas inteligentes e IA en diseño</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>PRY-117</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>STEAM and Gender: Strengthening the trajectories of girls and young people from public schools in Villa Alemana, Chile</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Juan Carlos Jeldes Pontio</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Medios de aprendizaje en arquitectura y diseño</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>PRY-118</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Seminario &amp; Workshop Belgica: Crafting Methods in Design Research</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Daniela Salgado Cofré, Álvaro Mercado Jara</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Métodos de diseño</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>PRY-119</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Actores, prácticas e impactos de las geografías de la financiarización urbana en Chile. Fondecyt nº 622656</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Adriana Marín Toro</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Vivienda, financiarización y políticas habitacionales</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>PRY-120</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Artifacts of Entanglement: In the Web of Extractive Urbanization</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Daniela Salgado Cofré, Álvaro Mercado Jara</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Urbanización, urbanismo y ecología política</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>PRY-121</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>CLIMATIC PLURIVERSES: A DECOLONIAL PERSPECTIVE OF GEOHUMANITIES FOR THE DESIGN OF ALTERNATIVE TERRITORIES IN CONTEXTS OF CLIMATE CHANGE (cod: ATE230072)</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Álvaro Mercado Jara</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Perspectivas decoloniales</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>PRY-122</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Capilla del Sagrado Corazón de Jesús</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Jorge Ferrada Herrera</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Patrimonio arquitectónico y rehabilitación</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>PRY-123</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Chile es un Archipiélago. La poesía y los mares de América.</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Jaime Reyes Gil</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Poesía y oficio</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>PRY-124</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>El espacio como criterio de interpretación del proyecto urbano: tres proyectos de la Escuela de Arquitectura de la UCV (1952-1970)</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Anna Braghini</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Teoría e historia de la arquitectura</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>PRY-125</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Entre Páginas y Dibujos: Revelando el Patrimonio Cultural de los Cuadernos-Bitácora de la Escuela de Arquitectura y Diseño PUCV</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Jaime Reyes Gil</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Acervo histórico de Ciudad Abierta y de la Escuela de Arquitectura y Diseño</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>PRY-126</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Huellas de luz</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Óscar Andrade Castro</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Arquitectura como medio didáctico</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>PRY-127</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Re-imaginar la escuela: Reflexiones sobre la arquitectura escolar moderna en Chile (1940-1980)</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Ursula Exss Cid</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Reforma escolar y enseñanza de la arquitectura</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>PRY-128</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Socialización del proyecto de un Parque para la infancia en el Barrio Puerto. Fondo Vinculacion con el Medio</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Rodrigo Saavedra Venegas</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Espacios de estimulación temprana</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>PRY-129</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>TEAsy Life: Modelo de IA para apoyar la autonomía de personas adultas con transtorno del espectro autista en el hogar</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Katherine Exss Cid</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Sistemas inteligentes e IA en diseño</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>PRY-130</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Taller Urbanismo Afectivo</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Emanuela Di Felice</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Urbanismo afectivo, deriva y reuso del patrimonio</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>PRY-131</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Umbral Comunitario: Creación arquitectónica de un espacio público de cuidados mediante la flexibilidad, la modulación y la extensibilidad de interior a exterior.</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Rodrigo Saavedra Venegas, Anna Braghini</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Movilidad, infraestructura urbana y equipamiento</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>PRY-132</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Accediendo a la zona de confort: Estudio sobre sistemas personales de confort térmico en personas con discapacidad intelectual en Chile</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Katherine Exss Cid</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Confort, bienestar y habitabilidad personal</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>PRY-133</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Chile va a la escuela: arquitectura escolar chilena, siglo XX</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Ursula Exss Cid</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Reforma escolar y enseñanza de la arquitectura</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>PRY-134</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Construyendo identidades a través de los objetos: Narrativas políticas y materiales en la artesanía chilena entre 1970 y 1990. Folio 039.737/2025</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Daniela Salgado Cofré</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Diseño social, territorial y patrimonio cultural</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>PRY-135</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>DECOLONIAL ANIMAL GEOGRAPHIES FROM THE SOUTH: MULTI-SPECIES TRAJECTORIES THROUGH THE ANDES IN THE CONTEXT OF ENVIRONMENTAL CHANGE 1252155</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Daniela Salgado Cofré</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Perspectivas decoloniales</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>PRY-136</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>El jardín y la escultura</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Ursula Exss Cid</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Arte y arquitectura</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>PRY-137</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Entramados Materiales en Territorios de Extractivismo</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Daniela Salgado Cofré</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Urbanización, urbanismo y ecología política</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>PRY-138</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>La Población Vergara en Viña del Mar como lugar de experimentación tipológica (1950-1980): manzana, trama y barrio.</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Anna Braghini</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Arquitectura moderna y habitar latinoamericano</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>PRY-139</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>La ciudad en juego</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Emanuela Di Felice</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Investigación-acción y artes urbanas</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>PRY-140</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Planificación y Paisajes Comunes en el Norte Chico de Chile: Agenciamientos más que urbanos en comunidades agrícolas</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Álvaro Mercado Jara</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Comunes, comunalidad y resiliencias socioecológicas</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>PRY-141</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Plataforma Omnidireccional de Realidad Virtual para la simulación de Movilidad y Respuesta Sensorial con Sistemas Hápticos, para el diseño y desarrollo de entornos formativos seguros y el desarrollo de líneas de investigación</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Katherine Exss Cid</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Accesibilidad e inclusión</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>PRY-142</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Prototipo de libro ilustrado "Reimaginar la escuela"</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Ursula Exss Cid</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Reforma escolar y enseñanza de la arquitectura</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Fundamentos disciplinares</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>PRY-143</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Proyecto de Revitalización del Sistema de Ascensores para el Desarrollo Sostenible de Valparaíso</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Lorena Herrera Ponce</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Movilidad, infraestructura urbana y equipamiento</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>PRY-144</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Arquitectura leve para el rito mariano itinerante del Valle del Choapa</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Álvaro Mercado Jara</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Diseño social, territorial y patrimonio cultural</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>PRY-145</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Artefactos Relacionales: Laboratorio en Diseño y Participación.</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Daniela Salgado Cofré</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Prácticas colectivas</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>PRY-146</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Cuerpos de niebla: Artefactos portables para captación de camanchaca</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Álvaro Mercado Jara</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Comunes, comunalidad y resiliencias socioecológicas</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>PRY-147</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>El atlas como artefacto narrativo de los entramados pos-extractivos transoceánicos</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Álvaro Mercado Jara</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Urbanización, urbanismo y ecología política</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>PRY-148</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Extractivismo artesanal: Utilización de la artesanía tradicional chilena desde la política y el diseño (1970-2000) 11260642</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Daniela Salgado Cofré</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Diseño social, territorial y patrimonio cultural</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>PRY-149</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Imaginarios Colectivos de Niebla</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Álvaro Mercado Jara</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Comunes, comunalidad y resiliencias socioecológicas</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>PRY-150</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Trayectorias populares, cuidados y producción del hábitat en procesos de radicación urbana en Reñaca Alto Sur, Gran Valparaíso</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Emanuela Di Felice</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Vivienda, financiarización y políticas habitacionales</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>teórico</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>PRY-151</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Workshop HAbitar Franciscano</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Emanuela Di Felice</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Patrimonio arquitectónico y rehabilitación</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>baja</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>PRY-152</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>infralab: exploraciones visuales y narrativas sobre infraestructura social e imaginarios de futuro</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Emanuela Di Felice</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Investigación-acción y artes urbanas</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Prácticas proyectuales</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>proyectual</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="E5:E457" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>SublineaNombres</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -5145,7 +12854,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -5176,17 +12884,17 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Investigación acerca del proyecto de arquitectura y de diseño: cómo se forma, cómo se ejerce como oficio y desde qué teoría e historia se piensa. Acervo de la e[ad] y Ciudad Abierta, historia y crítica de la arquitectura y del diseño, teoría del proyecto y sus categorías (hospitalidad, vacío, palabra poética), espacios y medios del aprendizaje, métodos de diseño, interacción, accesibilidad, fabricación y tecnologías. Forma a quienes enseñarán arquitectura y diseño. Polo teórico e histórico y polo proyectual.</t>
+          <t>Investigación acerca del proyecto de arquitectura y de diseño: los fundamentos sobre los que se funda la disciplina (su historia, su teoría, su filosofía y sus métodos) y el modo en que se dominan y se transmiten en la formación. Acervo de la e[ad] y Ciudad Abierta, historia y crítica de la arquitectura y del diseño, teoría del proyecto y sus categorías (hospitalidad, vacío, palabra poética), espacios y medios del aprendizaje, métodos de diseño, interacción, accesibilidad, fabricación y tecnologías. Forma a quienes enseñarán arquitectura y diseño. Polo teórico e histórico y polo proyectual.</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>propuesta 2026</t>
+          <t>nombre adoptado 29 sep 2026</t>
         </is>
       </c>
     </row>
@@ -5198,17 +12906,17 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Proyecto, ciudad y ecologías del territorio</t>
+          <t>Prácticas proyectuales</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Investigación a través del proyecto de arquitectura y de diseño sobre la ciudad, el territorio y sus ecologías: urbanización, ecología política, vivienda, patrimonio, borde costero, infraestructura y equipamiento, prácticas colectivas, urbanismo afectivo, diseño social y territorial. Polo teórico (teoría urbana, ecología política, vivienda) y polo proyectual (intervención, equipamiento, investigación-acción, creación de obra).</t>
+          <t>Investigación a través del proyecto de arquitectura y de diseño: obra nueva (un edificio, un espacio público, un objeto, un servicio, un sistema) que se inscribe en un contexto y lo modifica, con la ciudad, el territorio y sus ecologías como campo principal: urbanización, ecología política, vivienda, patrimonio, borde costero, infraestructura y equipamiento, prácticas colectivas, urbanismo afectivo, diseño social y territorial. Polo teórico (teoría urbana, ecología política, vivienda) y polo proyectual (equipamiento, investigación-acción, creación de obra).</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>propuesta 2026</t>
+          <t>nombre adoptado 6 oct 2026</t>
         </is>
       </c>
     </row>
@@ -5229,6 +12937,577 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" style="24" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>20 · Productividad por profesor (2014-2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Conteo de publicaciones y proyectos declarados por cada profesor; un proyecto compartido cuenta para cada participante. Fuente: Levantamiento de productividad 2014-2026 (planilla del equipo, oct 2026). Las publicaciones no distinguen indexación: para WoS/Scopus y capítulos con referato ver propuesta-dos-lineas.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>investigador</t>
+        </is>
+      </c>
+      <c r="B4" s="30" t="inlineStr">
+        <is>
+          <t>publicaciones_2014_2026</t>
+        </is>
+      </c>
+      <c r="C4" s="30" t="inlineStr">
+        <is>
+          <t>publicaciones_2022_2026</t>
+        </is>
+      </c>
+      <c r="D4" s="30" t="inlineStr">
+        <is>
+          <t>proyectos_2014_2026</t>
+        </is>
+      </c>
+      <c r="E4" s="30" t="inlineStr">
+        <is>
+          <t>proyectos_2022_2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Adriana Marín Toro</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Alejandro Garretón</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Alfred Thiers Jusan</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Andrés Garcés Alzamora</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Anna Braghini</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>19</v>
+      </c>
+      <c r="C9" t="n">
+        <v>14</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Arturo Chicano Jiménez</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Daniela Salgado Cofré</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>17</v>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="n">
+        <v>19</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>David Luza Cornejo</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Emanuela Di Felice</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>32</v>
+      </c>
+      <c r="C13" t="n">
+        <v>16</v>
+      </c>
+      <c r="D13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Erick Caro</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Herbert Spencer González</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>32</v>
+      </c>
+      <c r="C15" t="n">
+        <v>17</v>
+      </c>
+      <c r="D15" t="n">
+        <v>19</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Isabel M. Reyes</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Iván Ivelic Yanes</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Jaime Reyes Gil</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>19</v>
+      </c>
+      <c r="C18" t="n">
+        <v>7</v>
+      </c>
+      <c r="D18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Jorge Ferrada Herrera</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Juan Carlos Jeldes Pontio</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>12</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Katherine Exss Cid</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>30</v>
+      </c>
+      <c r="C21" t="n">
+        <v>21</v>
+      </c>
+      <c r="D21" t="n">
+        <v>15</v>
+      </c>
+      <c r="E21" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Leonardo Aravena</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Lorena Herrera Ponce</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>6</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Manuel Sanfuentes</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>6</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Marcelo Araya Aravena</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>6</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Michèle Wilkomirsky Uribe</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>11</v>
+      </c>
+      <c r="C26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>6</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Rodrigo Saavedra Venegas</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>10</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>9</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Sylvia Arriagada Cordero</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ursula Exss Cid</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>21</v>
+      </c>
+      <c r="C29" t="n">
+        <v>11</v>
+      </c>
+      <c r="D29" t="n">
+        <v>11</v>
+      </c>
+      <c r="E29" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Álvaro Mercado Jara</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>18</v>
+      </c>
+      <c r="C30" t="n">
+        <v>13</v>
+      </c>
+      <c r="D30" t="n">
+        <v>17</v>
+      </c>
+      <c r="E30" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Óscar Andrade Castro</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>9</v>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>9</v>
+      </c>
+      <c r="E31" t="n">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5263,7 +13542,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -5309,7 +13587,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -5337,7 +13615,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -5365,7 +13643,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -5393,7 +13671,7 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Proyecto, ciudad y ecologías del territorio</t>
+          <t>Prácticas proyectuales</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -5421,7 +13699,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Proyecto, ciudad y ecologías del territorio</t>
+          <t>Prácticas proyectuales</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -5449,7 +13727,7 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -5481,7 +13759,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -5509,7 +13787,7 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -5537,7 +13815,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -5569,7 +13847,7 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -5597,7 +13875,7 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -5625,7 +13903,7 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -5653,7 +13931,7 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -5681,7 +13959,7 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
@@ -5713,7 +13991,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -5745,7 +14023,7 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -5777,7 +14055,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -5805,7 +14083,7 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -5833,7 +14111,7 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -5865,7 +14143,7 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -5893,7 +14171,7 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Proyecto, ciudad y ecologías del territorio</t>
+          <t>Prácticas proyectuales</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -5925,7 +14203,7 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Proyecto, ciudad y ecologías del territorio</t>
+          <t>Prácticas proyectuales</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -5957,7 +14235,7 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -5989,7 +14267,7 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
@@ -6021,7 +14299,7 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
@@ -6049,7 +14327,7 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -6077,7 +14355,7 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
@@ -6105,7 +14383,7 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Proyecto, ciudad y ecologías del territorio</t>
+          <t>Prácticas proyectuales</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
@@ -6133,7 +14411,7 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Proyecto, ciudad y ecologías del territorio</t>
+          <t>Prácticas proyectuales</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
@@ -6161,7 +14439,7 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Proyecto, ciudad y ecologías del territorio</t>
+          <t>Prácticas proyectuales</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -6189,7 +14467,7 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Proyecto, ciudad y ecologías del territorio</t>
+          <t>Prácticas proyectuales</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -6221,7 +14499,7 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Proyecto, ciudad y ecologías del territorio</t>
+          <t>Prácticas proyectuales</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -6253,7 +14531,7 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Proyecto, ciudad y ecologías del territorio</t>
+          <t>Prácticas proyectuales</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -6285,7 +14563,7 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Proyecto, ciudad y ecologías del territorio</t>
+          <t>Prácticas proyectuales</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -6317,7 +14595,7 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Proyecto, ciudad y ecologías del territorio</t>
+          <t>Prácticas proyectuales</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -6349,7 +14627,7 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Proyecto, ciudad y ecologías del territorio</t>
+          <t>Prácticas proyectuales</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -6381,7 +14659,7 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>Proyecto, ciudad y ecologías del territorio</t>
+          <t>Prácticas proyectuales</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
@@ -6413,7 +14691,7 @@
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Proyecto, ciudad y ecologías del territorio</t>
+          <t>Prácticas proyectuales</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -6445,7 +14723,7 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>Proyecto, ciudad y ecologías del territorio</t>
+          <t>Prácticas proyectuales</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -6477,7 +14755,7 @@
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Proyecto, ciudad y ecologías del territorio</t>
+          <t>Prácticas proyectuales</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
@@ -6509,7 +14787,7 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
@@ -6541,7 +14819,7 @@
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
@@ -6573,7 +14851,7 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
@@ -6605,7 +14883,7 @@
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Proyecto, ciudad y ecologías del territorio</t>
+          <t>Prácticas proyectuales</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
@@ -6637,7 +14915,7 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>Proyecto, ciudad y ecologías del territorio</t>
+          <t>Prácticas proyectuales</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
@@ -6669,7 +14947,7 @@
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
@@ -6701,7 +14979,7 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
@@ -6733,7 +15011,7 @@
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
@@ -6765,7 +15043,7 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
@@ -6797,7 +15075,7 @@
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
@@ -6829,7 +15107,7 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
@@ -6861,7 +15139,7 @@
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
@@ -6893,7 +15171,7 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>Formación, oficio y teoría del proyecto</t>
+          <t>Fundamentos disciplinares</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
@@ -7373,7 +15651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="24" min="1" max="1"/>
@@ -8100,6 +16378,116 @@
       <c r="I26" t="inlineStr">
         <is>
           <t>consolidado por lectura detallada</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>INV-MSF</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Manuel Sanfuentes</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>FCT</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>agregado oct 2026 desde levantamiento de productividad; área y temas por confirmar</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>INV-IMR</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Isabel M. Reyes</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>FCT</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>agregado oct 2026 desde levantamiento de productividad; área y temas por confirmar</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>INV-AGR</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Alejandro Garretón</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>FCT</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>agregado oct 2026 desde levantamiento de productividad; área y temas por confirmar</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>INV-LAV</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Leonardo Aravena</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>FCT</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>agregado oct 2026 desde levantamiento de productividad; área y temas por confirmar</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>INV-ECR</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Erick Caro</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ECH</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>agregado oct 2026 desde levantamiento de productividad; área y temas por confirmar</t>
         </is>
       </c>
     </row>
@@ -8118,7 +16506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C158"/>
+  <dimension ref="A1:C166"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" style="24" min="1" max="1"/>
@@ -10772,6 +19160,142 @@
       <c r="C158" t="inlineStr">
         <is>
           <t>IA como material de diseño</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Poesía y oficio</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Manuel Sanfuentes</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Obra poética de Godofredo Iommi</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Travesías y geopoética</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Manuel Sanfuentes</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Traducción de Amereida</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Travesías y geopoética</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Isabel M. Reyes</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Traducción de Amereida</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Comunicación visual, diseño editorial y exposición material</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Alejandro Garretón</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Tipografía y grabado en la formación del diseño gráfico</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Fundamentos poéticos y artísticos del diseño</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Alejandro Garretón</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Referencias artísticas del campo del diseño</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Máquinas expresivas, algoritmos y arte tecnológico</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Leonardo Aravena</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Dispositivos de interacción física</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Medios de aprendizaje en arquitectura y diseño</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Leonardo Aravena</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Aprendizaje con tecnologías de interacción</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Saberes técnicos análogos</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Erick Caro</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Prefabricación monomaterial para vivienda económica</t>
         </is>
       </c>
     </row>

--- a/mad-map-data-v2.xlsx
+++ b/mad-map-data-v2.xlsx
@@ -636,7 +636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="24" min="1" max="1"/>
@@ -657,6 +657,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="16" customHeight="1" s="24">
       <c r="A4" s="26" t="inlineStr">
         <is>
@@ -672,19 +673,19 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Estructura superior. Lo que la Escuela declara y sostiene. BORRADOR.</t>
+          <t>Estructura superior: Fundamentos disciplinares (acerca del proyecto) y Prácticas proyectuales (a través del proyecto), cada una con polo teórico y polo proyectual.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Sublínea (~30)</t>
+          <t>Sublínea (53)</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Pertenece a UNA sola Línea. Granularidad operativa. Banco depurado.</t>
+          <t>Pertenece a UNA sola Línea y a un polo (teórico o proyectual). Granularidad operativa.</t>
         </is>
       </c>
     </row>
@@ -760,80 +761,93 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="16" customHeight="1" s="24">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Proyecto</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Proyecto de investigación o creación 2014-2026 (hoja 19_Proyectos). Pertenece a una Sublínea; participan uno o más Investigadores. La productividad por profesor está en 20_Productividad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="inlineStr">
         <is>
           <t>Convenciones</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>BORRADOR (fondo amarillo)</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Filas/celdas con valores propuestos por revisar. La Línea-04 y los mapeos m:n están sujetos a curaduría.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>IDs</t>
+          <t>BORRADOR (fondo amarillo)</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>LIN-NN, SUB-NN, TEM-NNN, INV-NN, LAB-XXX, MOD-NN, SAL-XXX. Estables — no renombrar tras enlazar.</t>
+          <t>Filas o celdas con valores propuestos por revisar. Los mapeos m:n y la asignación de proyectos a sublíneas (19_Proyectos) están sujetos a curaduría.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Cardinalidad Sublínea→Línea</t>
+          <t>IDs</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>1:N estricta (una Sublínea pertenece a UNA Línea). Cambia el linea_id si el ajuste lo amerita.</t>
+          <t>LIN-NN, SUB-NN, TEM-NNN, INV-NN, LAB-XXX, MOD-NN, SAL-XXX. Estables — no renombrar tras enlazar.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Cardinalidad Tema→Sublínea</t>
+          <t>Cardinalidad Sublínea→Línea</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>M:N (un Tema puede colgar de varias Sublíneas). Editar en la hoja 08_Temas (cada fila atribuye un tema a una sublínea y un investigador).</t>
+          <t>1:N estricta (una Sublínea pertenece a UNA Línea). Cambia el linea_id si el ajuste lo amerita.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Cardinalidad Lab→Línea</t>
+          <t>Cardinalidad Tema→Sublínea</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>M:N. Un Lab puede sostener varias Líneas. Editar en 10_Lab_Linea.</t>
+          <t>M:N (un Tema puede colgar de varias Sublíneas). Editar en la hoja 08_Temas (cada fila atribuye un tema a una sublínea y un investigador).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
+          <t>Cardinalidad Lab→Línea</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>M:N. Un Lab puede sostener varias Líneas. Editar en 10_Lab_Linea.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
           <t>Decisiones pendientes</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Hoja 15_Decisiones — preguntas abiertas que afectan el modelo.</t>
         </is>
@@ -2270,7 +2284,7 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>¿3 o 4 Líneas troncales?</t>
+          <t>¿Cuántas líneas de investigación?</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -2341,7 +2355,7 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Asignada provisoriamente a LIN-02. Tiene respaldo también en LIN-03. Decidir hogar.</t>
+          <t>Asignada a Prácticas proyectuales (polo proyectual). Tiene respaldo también en Fundamentos disciplinares por el acervo de las travesías. Decidir si queda como puente entre líneas.</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -2363,7 +2377,7 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Asignada provisoriamente a LIN-02 (ecologías). Podría leerse en LIN-01 (inclusión) o quedar transversal.</t>
+          <t>Asignada a Prácticas proyectuales (polo teórico). Podría leerse también en Fundamentos disciplinares (diseño decolonial) o quedar transversal.</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
@@ -2779,6 +2793,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -2807,7 +2822,7 @@
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>El doctorado forma investigadores para quienes la obra es origen y prueba de la tesis. Esa obra, sea edificada, fabricada, escrita o dibujada, vale como argumento por sí misma, y el discurso doctoral se construye para hacerla legible y discutible. La pregunta que esa obra está llamada a argumentar es la que el programa hace suya: cómo reinventar el habitar humano, y la responde desde el habitar poético que funda a la Escuela. Las dos líneas del doctorado investigan ese habitar en arquitectura y en diseño: una investiga acerca del proyecto, su formación, su oficio y su teoría; la otra investiga a través del proyecto, sobre la ciudad, el territorio y sus ecologías. Cada línea lleva dentro su contraparte, teórica o proyectual. Doctorarse aquí es haber producido una obra capaz de sostener esos principios al ponerse a prueba y, en su mejor versión, capaz de reformularlos.</t>
+          <t>El doctorado forma investigadores para quienes la obra es origen y prueba de la tesis. Esa obra, sea edificada, fabricada, escrita o dibujada, vale como argumento por sí misma, y el discurso doctoral se construye para hacerla legible y discutible. La pregunta que esa obra está llamada a argumentar es la que el programa hace suya: cómo reinventar el habitar humano, y la responde desde el habitar poético que funda a la Escuela. Las dos líneas del doctorado investigan ese habitar en arquitectura y en diseño: Fundamentos disciplinares investiga acerca del proyecto, lo que sostiene a la disciplina y cómo se transmite; Prácticas proyectuales investiga a través del proyecto, como obra nueva que se inscribe en un contexto y lo modifica. Cada línea lleva dentro su contraparte, teórica o proyectual. Doctorarse aquí es haber producido una obra capaz de sostener esos principios al ponerse a prueba y, en su mejor versión, capaz de reformularlos.</t>
         </is>
       </c>
     </row>
@@ -12831,26 +12846,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="24" min="1" max="1"/>
     <col width="55" customWidth="1" style="24" min="2" max="2"/>
     <col width="95" customWidth="1" style="24" min="3" max="3"/>
     <col width="26" customWidth="1" style="24" min="4" max="4"/>
+    <col width="60" customWidth="1" style="24" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" s="24">
       <c r="A1" s="25" t="inlineStr">
         <is>
-          <t>01 · Líneas de investigación (2, propuesta septiembre 2026)</t>
+          <t>01 · Líneas de investigación (2, nombres adoptados en octubre de 2026)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="23" t="inlineStr">
         <is>
-          <t>Cada Sublínea pertenece a una Línea y a un polo (teórico | proyectual). Los Laboratorios pueden sostener una o varias Líneas.</t>
+          <t>Dos líneas simétricas, cada una con polo teórico y polo proyectual. Cada Sublínea pertenece a una Línea y a un polo. 'bajada' es la definición breve que muestra la visualización; 'descripción' es el alcance completo.</t>
         </is>
       </c>
     </row>
@@ -12875,6 +12891,16 @@
           <t>estado</t>
         </is>
       </c>
+      <c r="E4" s="30" t="inlineStr">
+        <is>
+          <t>modo</t>
+        </is>
+      </c>
+      <c r="F4" s="30" t="inlineStr">
+        <is>
+          <t>bajada</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="45" customHeight="1" s="24">
       <c r="A5" s="8" t="inlineStr">
@@ -12897,6 +12923,16 @@
           <t>nombre adoptado 29 sep 2026</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Investigación acerca del proyecto</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lo que sostiene a la disciplina (su historia, su teoría, su filosofía y sus métodos) y cómo se domina y se transmite en la formación.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="45" customHeight="1" s="24">
       <c r="A6" s="8" t="inlineStr">
@@ -12917,6 +12953,16 @@
       <c r="D6" s="8" t="inlineStr">
         <is>
           <t>nombre adoptado 6 oct 2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Investigación a través del proyecto</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Obra nueva (un edificio, un espacio público, un objeto, un servicio, un sistema) que se inscribe en un contexto y lo modifica.</t>
         </is>
       </c>
     </row>
